--- a/artfynd/A 3512-2026 artfynd.xlsx
+++ b/artfynd/A 3512-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,1470 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131359549</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stor-Kalvsberget Norra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>488161</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7036107</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131359546</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stor-Kalvsberget Norra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>488175</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7036216</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131359539</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58043</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stor-Kalvsberget Norra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>488192</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7036152</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 födosökande talltita i lämplig häckbiotop.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131359550</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stor-Kalvsberget Norra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>488109</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7036098</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131359541</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80255</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stor-Kalvsberget Norra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>488134</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7036157</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131359533</v>
+      </c>
+      <c r="B8" t="n">
+        <v>83226</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stor-Kalvsberget Norra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>488178</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7036174</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131359543</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stor-Kalvsberget Norra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>488218</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7036201</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131359553</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stor-Kalvsberget Norra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>488185</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7036084</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131359545</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stor-Kalvsberget Norra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>488254</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7036203</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131359548</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stor-Kalvsberget Norra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>488187</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7036101</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131359534</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stor-Kalvsberget Norra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>488052</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7036113</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131359547</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79246</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stor-Kalvsberget Norra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>488171</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7036186</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131359542</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79003</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stor-Kalvsberget Norra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>488198</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7036091</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3512-2026 artfynd.xlsx
+++ b/artfynd/A 3512-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>131359549</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>131359546</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>131359539</v>
       </c>
       <c r="B5" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>131359550</v>
       </c>
       <c r="B6" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>131359541</v>
       </c>
       <c r="B7" t="n">
-        <v>80255</v>
+        <v>80257</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>131359533</v>
       </c>
       <c r="B8" t="n">
-        <v>83226</v>
+        <v>83228</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>131359543</v>
       </c>
       <c r="B9" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>131359553</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>131359545</v>
       </c>
       <c r="B11" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>131359548</v>
       </c>
       <c r="B12" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>131359534</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>131359547</v>
       </c>
       <c r="B14" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>131359542</v>
       </c>
       <c r="B15" t="n">
-        <v>79003</v>
+        <v>79005</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 3512-2026 artfynd.xlsx
+++ b/artfynd/A 3512-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>131359549</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>131359546</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>131359539</v>
       </c>
       <c r="B5" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>131359550</v>
       </c>
       <c r="B6" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>131359541</v>
       </c>
       <c r="B7" t="n">
-        <v>80257</v>
+        <v>80258</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131359533</v>
+        <v>131359543</v>
       </c>
       <c r="B8" t="n">
-        <v>83228</v>
+        <v>79249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488178</v>
+        <v>488218</v>
       </c>
       <c r="R8" t="n">
-        <v>7036174</v>
+        <v>7036201</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,21 +1452,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1484,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131359543</v>
+        <v>131359533</v>
       </c>
       <c r="B9" t="n">
-        <v>79248</v>
+        <v>83229</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488218</v>
+        <v>488178</v>
       </c>
       <c r="R9" t="n">
-        <v>7036201</v>
+        <v>7036174</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,6 +1558,21 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1593,7 +1593,7 @@
         <v>131359553</v>
       </c>
       <c r="B10" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>131359545</v>
       </c>
       <c r="B11" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>131359548</v>
       </c>
       <c r="B12" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>131359534</v>
       </c>
       <c r="B13" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131359547</v>
+        <v>131359542</v>
       </c>
       <c r="B14" t="n">
-        <v>79248</v>
+        <v>79006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488171</v>
+        <v>488198</v>
       </c>
       <c r="R14" t="n">
-        <v>7036186</v>
+        <v>7036091</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,6 +2127,21 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2144,10 +2159,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131359542</v>
+        <v>131359547</v>
       </c>
       <c r="B15" t="n">
-        <v>79005</v>
+        <v>79249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2155,21 +2170,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2182,10 +2197,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488198</v>
+        <v>488171</v>
       </c>
       <c r="R15" t="n">
-        <v>7036091</v>
+        <v>7036186</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2233,21 +2248,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 3512-2026 artfynd.xlsx
+++ b/artfynd/A 3512-2026 artfynd.xlsx
@@ -1363,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131359543</v>
+        <v>131359533</v>
       </c>
       <c r="B8" t="n">
-        <v>79249</v>
+        <v>83229</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488218</v>
+        <v>488178</v>
       </c>
       <c r="R8" t="n">
-        <v>7036201</v>
+        <v>7036174</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,6 +1452,21 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1469,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131359533</v>
+        <v>131359543</v>
       </c>
       <c r="B9" t="n">
-        <v>83229</v>
+        <v>79249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488178</v>
+        <v>488218</v>
       </c>
       <c r="R9" t="n">
-        <v>7036174</v>
+        <v>7036201</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,21 +1573,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 3512-2026 artfynd.xlsx
+++ b/artfynd/A 3512-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>131359549</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>131359546</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>131359539</v>
       </c>
       <c r="B5" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>131359550</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>131359541</v>
       </c>
       <c r="B7" t="n">
-        <v>80258</v>
+        <v>80259</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131359533</v>
+        <v>131359543</v>
       </c>
       <c r="B8" t="n">
-        <v>83229</v>
+        <v>79250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488178</v>
+        <v>488218</v>
       </c>
       <c r="R8" t="n">
-        <v>7036174</v>
+        <v>7036201</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,21 +1452,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1484,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131359543</v>
+        <v>131359533</v>
       </c>
       <c r="B9" t="n">
-        <v>79249</v>
+        <v>83230</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488218</v>
+        <v>488178</v>
       </c>
       <c r="R9" t="n">
-        <v>7036201</v>
+        <v>7036174</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,6 +1558,21 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1593,7 +1593,7 @@
         <v>131359553</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>131359545</v>
       </c>
       <c r="B11" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>131359548</v>
       </c>
       <c r="B12" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>131359534</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131359542</v>
+        <v>131359547</v>
       </c>
       <c r="B14" t="n">
-        <v>79006</v>
+        <v>79250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488198</v>
+        <v>488171</v>
       </c>
       <c r="R14" t="n">
-        <v>7036091</v>
+        <v>7036186</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,21 +2127,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2159,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131359547</v>
+        <v>131359542</v>
       </c>
       <c r="B15" t="n">
-        <v>79249</v>
+        <v>79007</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,21 +2155,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2197,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488171</v>
+        <v>488198</v>
       </c>
       <c r="R15" t="n">
-        <v>7036186</v>
+        <v>7036091</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2248,6 +2233,21 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 3512-2026 artfynd.xlsx
+++ b/artfynd/A 3512-2026 artfynd.xlsx
@@ -1696,7 +1696,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131359545</v>
+        <v>131359548</v>
       </c>
       <c r="B11" t="n">
         <v>79250</v>
@@ -1734,10 +1734,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488254</v>
+        <v>488187</v>
       </c>
       <c r="R11" t="n">
-        <v>7036203</v>
+        <v>7036101</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131359548</v>
+        <v>131359545</v>
       </c>
       <c r="B12" t="n">
         <v>79250</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488187</v>
+        <v>488254</v>
       </c>
       <c r="R12" t="n">
-        <v>7036101</v>
+        <v>7036203</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 3512-2026 artfynd.xlsx
+++ b/artfynd/A 3512-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>131359549</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>131359546</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>131359539</v>
       </c>
       <c r="B5" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>131359550</v>
       </c>
       <c r="B6" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>131359541</v>
       </c>
       <c r="B7" t="n">
-        <v>80259</v>
+        <v>80262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>131359543</v>
       </c>
       <c r="B8" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>131359533</v>
       </c>
       <c r="B9" t="n">
-        <v>83230</v>
+        <v>83233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>131359553</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131359548</v>
+        <v>131359545</v>
       </c>
       <c r="B11" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1734,10 +1734,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488187</v>
+        <v>488254</v>
       </c>
       <c r="R11" t="n">
-        <v>7036101</v>
+        <v>7036203</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131359545</v>
+        <v>131359548</v>
       </c>
       <c r="B12" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488254</v>
+        <v>488187</v>
       </c>
       <c r="R12" t="n">
-        <v>7036203</v>
+        <v>7036101</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1911,7 +1911,7 @@
         <v>131359534</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>131359547</v>
       </c>
       <c r="B14" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>131359542</v>
       </c>
       <c r="B15" t="n">
-        <v>79007</v>
+        <v>79010</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 3512-2026 artfynd.xlsx
+++ b/artfynd/A 3512-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>131359549</v>
       </c>
       <c r="B3" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>131359546</v>
       </c>
       <c r="B4" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>131359539</v>
       </c>
       <c r="B5" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>131359550</v>
       </c>
       <c r="B6" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>131359541</v>
       </c>
       <c r="B7" t="n">
-        <v>80262</v>
+        <v>80263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>131359543</v>
       </c>
       <c r="B8" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>131359533</v>
       </c>
       <c r="B9" t="n">
-        <v>83233</v>
+        <v>83234</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>131359553</v>
       </c>
       <c r="B10" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>131359545</v>
       </c>
       <c r="B11" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>131359548</v>
       </c>
       <c r="B12" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>131359534</v>
       </c>
       <c r="B13" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>131359547</v>
       </c>
       <c r="B14" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>131359542</v>
       </c>
       <c r="B15" t="n">
-        <v>79010</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 3512-2026 artfynd.xlsx
+++ b/artfynd/A 3512-2026 artfynd.xlsx
@@ -1363,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131359543</v>
+        <v>131359533</v>
       </c>
       <c r="B8" t="n">
-        <v>79254</v>
+        <v>83234</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488218</v>
+        <v>488178</v>
       </c>
       <c r="R8" t="n">
-        <v>7036201</v>
+        <v>7036174</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,6 +1452,21 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1469,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131359533</v>
+        <v>131359543</v>
       </c>
       <c r="B9" t="n">
-        <v>83234</v>
+        <v>79254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488178</v>
+        <v>488218</v>
       </c>
       <c r="R9" t="n">
-        <v>7036174</v>
+        <v>7036201</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,21 +1573,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1696,7 +1696,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131359545</v>
+        <v>131359548</v>
       </c>
       <c r="B11" t="n">
         <v>79254</v>
@@ -1734,10 +1734,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488254</v>
+        <v>488187</v>
       </c>
       <c r="R11" t="n">
-        <v>7036203</v>
+        <v>7036101</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131359548</v>
+        <v>131359545</v>
       </c>
       <c r="B12" t="n">
         <v>79254</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488187</v>
+        <v>488254</v>
       </c>
       <c r="R12" t="n">
-        <v>7036101</v>
+        <v>7036203</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 3512-2026 artfynd.xlsx
+++ b/artfynd/A 3512-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>131359549</v>
       </c>
       <c r="B3" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>131359546</v>
       </c>
       <c r="B4" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>131359539</v>
       </c>
       <c r="B5" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>131359550</v>
       </c>
       <c r="B6" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>131359541</v>
       </c>
       <c r="B7" t="n">
-        <v>80263</v>
+        <v>80269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>131359533</v>
       </c>
       <c r="B8" t="n">
-        <v>83234</v>
+        <v>83240</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>131359543</v>
       </c>
       <c r="B9" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>131359553</v>
       </c>
       <c r="B10" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131359548</v>
+        <v>131359545</v>
       </c>
       <c r="B11" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1734,10 +1734,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488187</v>
+        <v>488254</v>
       </c>
       <c r="R11" t="n">
-        <v>7036101</v>
+        <v>7036203</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131359545</v>
+        <v>131359548</v>
       </c>
       <c r="B12" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488254</v>
+        <v>488187</v>
       </c>
       <c r="R12" t="n">
-        <v>7036203</v>
+        <v>7036101</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1911,7 +1911,7 @@
         <v>131359534</v>
       </c>
       <c r="B13" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>131359547</v>
       </c>
       <c r="B14" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>131359542</v>
       </c>
       <c r="B15" t="n">
-        <v>79011</v>
+        <v>79017</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 3512-2026 artfynd.xlsx
+++ b/artfynd/A 3512-2026 artfynd.xlsx
@@ -1363,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131359533</v>
+        <v>131359543</v>
       </c>
       <c r="B8" t="n">
-        <v>83240</v>
+        <v>79260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488178</v>
+        <v>488218</v>
       </c>
       <c r="R8" t="n">
-        <v>7036174</v>
+        <v>7036201</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,21 +1452,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1484,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131359543</v>
+        <v>131359533</v>
       </c>
       <c r="B9" t="n">
-        <v>79260</v>
+        <v>83240</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488218</v>
+        <v>488178</v>
       </c>
       <c r="R9" t="n">
-        <v>7036201</v>
+        <v>7036174</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,6 +1558,21 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131359547</v>
+        <v>131359542</v>
       </c>
       <c r="B14" t="n">
-        <v>79260</v>
+        <v>79017</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488171</v>
+        <v>488198</v>
       </c>
       <c r="R14" t="n">
-        <v>7036186</v>
+        <v>7036091</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,6 +2127,21 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2144,10 +2159,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131359542</v>
+        <v>131359547</v>
       </c>
       <c r="B15" t="n">
-        <v>79017</v>
+        <v>79260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2155,21 +2170,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2182,10 +2197,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488198</v>
+        <v>488171</v>
       </c>
       <c r="R15" t="n">
-        <v>7036091</v>
+        <v>7036186</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2233,21 +2248,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 3512-2026 artfynd.xlsx
+++ b/artfynd/A 3512-2026 artfynd.xlsx
@@ -2038,10 +2038,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131359542</v>
+        <v>131359547</v>
       </c>
       <c r="B14" t="n">
-        <v>79017</v>
+        <v>79260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488198</v>
+        <v>488171</v>
       </c>
       <c r="R14" t="n">
-        <v>7036091</v>
+        <v>7036186</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,21 +2127,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2159,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131359547</v>
+        <v>131359542</v>
       </c>
       <c r="B15" t="n">
-        <v>79260</v>
+        <v>79017</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,21 +2155,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2197,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488171</v>
+        <v>488198</v>
       </c>
       <c r="R15" t="n">
-        <v>7036186</v>
+        <v>7036091</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2248,6 +2233,21 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 3512-2026 artfynd.xlsx
+++ b/artfynd/A 3512-2026 artfynd.xlsx
@@ -1363,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131359543</v>
+        <v>131359533</v>
       </c>
       <c r="B8" t="n">
-        <v>79260</v>
+        <v>83240</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488218</v>
+        <v>488178</v>
       </c>
       <c r="R8" t="n">
-        <v>7036201</v>
+        <v>7036174</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,6 +1452,21 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1469,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131359533</v>
+        <v>131359543</v>
       </c>
       <c r="B9" t="n">
-        <v>83240</v>
+        <v>79260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488178</v>
+        <v>488218</v>
       </c>
       <c r="R9" t="n">
-        <v>7036174</v>
+        <v>7036201</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,21 +1573,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1696,7 +1696,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131359545</v>
+        <v>131359548</v>
       </c>
       <c r="B11" t="n">
         <v>79260</v>
@@ -1734,10 +1734,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488254</v>
+        <v>488187</v>
       </c>
       <c r="R11" t="n">
-        <v>7036203</v>
+        <v>7036101</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131359548</v>
+        <v>131359545</v>
       </c>
       <c r="B12" t="n">
         <v>79260</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488187</v>
+        <v>488254</v>
       </c>
       <c r="R12" t="n">
-        <v>7036101</v>
+        <v>7036203</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131359547</v>
+        <v>131359542</v>
       </c>
       <c r="B14" t="n">
-        <v>79260</v>
+        <v>79017</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488171</v>
+        <v>488198</v>
       </c>
       <c r="R14" t="n">
-        <v>7036186</v>
+        <v>7036091</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,6 +2127,21 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2144,10 +2159,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131359542</v>
+        <v>131359547</v>
       </c>
       <c r="B15" t="n">
-        <v>79017</v>
+        <v>79260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2155,21 +2170,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2182,10 +2197,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488198</v>
+        <v>488171</v>
       </c>
       <c r="R15" t="n">
-        <v>7036091</v>
+        <v>7036186</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2233,21 +2248,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 3512-2026 artfynd.xlsx
+++ b/artfynd/A 3512-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>131359549</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>131359546</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>131359539</v>
       </c>
       <c r="B5" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>131359550</v>
       </c>
       <c r="B6" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>131359541</v>
       </c>
       <c r="B7" t="n">
-        <v>80269</v>
+        <v>80270</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131359533</v>
+        <v>131359543</v>
       </c>
       <c r="B8" t="n">
-        <v>83240</v>
+        <v>79261</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488178</v>
+        <v>488218</v>
       </c>
       <c r="R8" t="n">
-        <v>7036174</v>
+        <v>7036201</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,21 +1452,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1484,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131359543</v>
+        <v>131359533</v>
       </c>
       <c r="B9" t="n">
-        <v>79260</v>
+        <v>83241</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488218</v>
+        <v>488178</v>
       </c>
       <c r="R9" t="n">
-        <v>7036201</v>
+        <v>7036174</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,6 +1558,21 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1593,7 +1593,7 @@
         <v>131359553</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>131359548</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>131359545</v>
       </c>
       <c r="B12" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>131359534</v>
       </c>
       <c r="B13" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131359542</v>
+        <v>131359547</v>
       </c>
       <c r="B14" t="n">
-        <v>79017</v>
+        <v>79261</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488198</v>
+        <v>488171</v>
       </c>
       <c r="R14" t="n">
-        <v>7036091</v>
+        <v>7036186</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,21 +2127,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2159,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131359547</v>
+        <v>131359542</v>
       </c>
       <c r="B15" t="n">
-        <v>79260</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,21 +2155,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2197,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488171</v>
+        <v>488198</v>
       </c>
       <c r="R15" t="n">
-        <v>7036186</v>
+        <v>7036091</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2248,6 +2233,21 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 3512-2026 artfynd.xlsx
+++ b/artfynd/A 3512-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>131359549</v>
       </c>
       <c r="B3" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>131359546</v>
       </c>
       <c r="B4" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>131359539</v>
       </c>
       <c r="B5" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>131359550</v>
       </c>
       <c r="B6" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>131359541</v>
       </c>
       <c r="B7" t="n">
-        <v>80270</v>
+        <v>80273</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>131359543</v>
       </c>
       <c r="B8" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>131359533</v>
       </c>
       <c r="B9" t="n">
-        <v>83241</v>
+        <v>83244</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>131359553</v>
       </c>
       <c r="B10" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>131359548</v>
       </c>
       <c r="B11" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>131359545</v>
       </c>
       <c r="B12" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>131359534</v>
       </c>
       <c r="B13" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131359547</v>
+        <v>131359542</v>
       </c>
       <c r="B14" t="n">
-        <v>79261</v>
+        <v>79021</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488171</v>
+        <v>488198</v>
       </c>
       <c r="R14" t="n">
-        <v>7036186</v>
+        <v>7036091</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,6 +2127,21 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2144,10 +2159,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131359542</v>
+        <v>131359547</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>79264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2155,21 +2170,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2182,10 +2197,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488198</v>
+        <v>488171</v>
       </c>
       <c r="R15" t="n">
-        <v>7036091</v>
+        <v>7036186</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2233,21 +2248,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 3512-2026 artfynd.xlsx
+++ b/artfynd/A 3512-2026 artfynd.xlsx
@@ -1696,7 +1696,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131359548</v>
+        <v>131359545</v>
       </c>
       <c r="B11" t="n">
         <v>79264</v>
@@ -1734,10 +1734,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488187</v>
+        <v>488254</v>
       </c>
       <c r="R11" t="n">
-        <v>7036101</v>
+        <v>7036203</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131359545</v>
+        <v>131359548</v>
       </c>
       <c r="B12" t="n">
         <v>79264</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488254</v>
+        <v>488187</v>
       </c>
       <c r="R12" t="n">
-        <v>7036203</v>
+        <v>7036101</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 3512-2026 artfynd.xlsx
+++ b/artfynd/A 3512-2026 artfynd.xlsx
@@ -1696,7 +1696,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131359545</v>
+        <v>131359548</v>
       </c>
       <c r="B11" t="n">
         <v>79264</v>
@@ -1734,10 +1734,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488254</v>
+        <v>488187</v>
       </c>
       <c r="R11" t="n">
-        <v>7036203</v>
+        <v>7036101</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131359548</v>
+        <v>131359545</v>
       </c>
       <c r="B12" t="n">
         <v>79264</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488187</v>
+        <v>488254</v>
       </c>
       <c r="R12" t="n">
-        <v>7036101</v>
+        <v>7036203</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131359542</v>
+        <v>131359547</v>
       </c>
       <c r="B14" t="n">
-        <v>79021</v>
+        <v>79264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488198</v>
+        <v>488171</v>
       </c>
       <c r="R14" t="n">
-        <v>7036091</v>
+        <v>7036186</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,21 +2127,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2159,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131359547</v>
+        <v>131359542</v>
       </c>
       <c r="B15" t="n">
-        <v>79264</v>
+        <v>79021</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,21 +2155,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2197,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488171</v>
+        <v>488198</v>
       </c>
       <c r="R15" t="n">
-        <v>7036186</v>
+        <v>7036091</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2248,6 +2233,21 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 3512-2026 artfynd.xlsx
+++ b/artfynd/A 3512-2026 artfynd.xlsx
@@ -1363,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131359543</v>
+        <v>131359533</v>
       </c>
       <c r="B8" t="n">
-        <v>79264</v>
+        <v>83244</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488218</v>
+        <v>488178</v>
       </c>
       <c r="R8" t="n">
-        <v>7036201</v>
+        <v>7036174</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,6 +1452,21 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1469,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131359533</v>
+        <v>131359543</v>
       </c>
       <c r="B9" t="n">
-        <v>83244</v>
+        <v>79264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488178</v>
+        <v>488218</v>
       </c>
       <c r="R9" t="n">
-        <v>7036174</v>
+        <v>7036201</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,21 +1573,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 3512-2026 artfynd.xlsx
+++ b/artfynd/A 3512-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>131359549</v>
       </c>
       <c r="B3" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>131359546</v>
       </c>
       <c r="B4" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>131359539</v>
       </c>
       <c r="B5" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>131359550</v>
       </c>
       <c r="B6" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>131359541</v>
       </c>
       <c r="B7" t="n">
-        <v>80273</v>
+        <v>80275</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>131359533</v>
       </c>
       <c r="B8" t="n">
-        <v>83244</v>
+        <v>83246</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>131359543</v>
       </c>
       <c r="B9" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>131359553</v>
       </c>
       <c r="B10" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>131359548</v>
       </c>
       <c r="B11" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>131359545</v>
       </c>
       <c r="B12" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>131359534</v>
       </c>
       <c r="B13" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>131359547</v>
       </c>
       <c r="B14" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>131359542</v>
       </c>
       <c r="B15" t="n">
-        <v>79021</v>
+        <v>79023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 3512-2026 artfynd.xlsx
+++ b/artfynd/A 3512-2026 artfynd.xlsx
@@ -1363,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131359533</v>
+        <v>131359543</v>
       </c>
       <c r="B8" t="n">
-        <v>83246</v>
+        <v>79266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488178</v>
+        <v>488218</v>
       </c>
       <c r="R8" t="n">
-        <v>7036174</v>
+        <v>7036201</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,21 +1452,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1484,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131359543</v>
+        <v>131359533</v>
       </c>
       <c r="B9" t="n">
-        <v>79266</v>
+        <v>83246</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,21 +1480,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488218</v>
+        <v>488178</v>
       </c>
       <c r="R9" t="n">
-        <v>7036201</v>
+        <v>7036174</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,6 +1558,21 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 3512-2026 artfynd.xlsx
+++ b/artfynd/A 3512-2026 artfynd.xlsx
@@ -1363,10 +1363,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131359543</v>
+        <v>131359533</v>
       </c>
       <c r="B8" t="n">
-        <v>79266</v>
+        <v>83246</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,21 +1374,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488218</v>
+        <v>488178</v>
       </c>
       <c r="R8" t="n">
-        <v>7036201</v>
+        <v>7036174</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,6 +1452,21 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1469,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131359533</v>
+        <v>131359543</v>
       </c>
       <c r="B9" t="n">
-        <v>83246</v>
+        <v>79266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488178</v>
+        <v>488218</v>
       </c>
       <c r="R9" t="n">
-        <v>7036174</v>
+        <v>7036201</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,21 +1573,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 3512-2026 artfynd.xlsx
+++ b/artfynd/A 3512-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90569298</v>
+        <v>131359543</v>
       </c>
       <c r="B2" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220204</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Husås – Andviken – väg Z751, Jmt</t>
+          <t>Stor-Kalvsberget Norra, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488363.8277805874</v>
+        <v>488218</v>
       </c>
       <c r="R2" t="n">
-        <v>7036217.050426256</v>
+        <v>7036201</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,27 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-07-12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-07-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Allmän</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,41 +757,38 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Leif Andersson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emma Karlsson, Therese Kalling</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131359549</v>
+        <v>131359545</v>
       </c>
       <c r="B3" t="n">
-        <v>79266</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -839,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488161</v>
+        <v>488254</v>
       </c>
       <c r="R3" t="n">
-        <v>7036107</v>
+        <v>7036203</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -910,11 +890,11 @@
         <v>131359546</v>
       </c>
       <c r="B4" t="n">
-        <v>79266</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1013,61 +993,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131359539</v>
+        <v>131359547</v>
       </c>
       <c r="B5" t="n">
-        <v>58063</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stor-Kalvsberget Norra, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488192</v>
+        <v>488171</v>
       </c>
       <c r="R5" t="n">
-        <v>7036152</v>
+        <v>7036186</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,17 +1069,13 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1 födosökande talltita i lämplig häckbiotop.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1136,14 +1099,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131359550</v>
+        <v>131359548</v>
       </c>
       <c r="B6" t="n">
-        <v>79266</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1174,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488109</v>
+        <v>488187</v>
       </c>
       <c r="R6" t="n">
-        <v>7036098</v>
+        <v>7036101</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,32 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131359541</v>
+        <v>131359549</v>
       </c>
       <c r="B7" t="n">
-        <v>80275</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488134</v>
+        <v>488161</v>
       </c>
       <c r="R7" t="n">
-        <v>7036157</v>
+        <v>7036107</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,21 +1294,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1363,14 +1311,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131359543</v>
+        <v>131359550</v>
       </c>
       <c r="B8" t="n">
-        <v>79266</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1401,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488218</v>
+        <v>488109</v>
       </c>
       <c r="R8" t="n">
-        <v>7036201</v>
+        <v>7036098</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,32 +1417,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131359533</v>
+        <v>131359553</v>
       </c>
       <c r="B9" t="n">
-        <v>83246</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1507,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488178</v>
+        <v>488185</v>
       </c>
       <c r="R9" t="n">
-        <v>7036174</v>
+        <v>7036084</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,21 +1506,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1590,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131359553</v>
+        <v>131359533</v>
       </c>
       <c r="B10" t="n">
-        <v>79266</v>
+        <v>83307</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,21 +1534,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1628,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488185</v>
+        <v>488178</v>
       </c>
       <c r="R10" t="n">
-        <v>7036084</v>
+        <v>7036174</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,6 +1612,21 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1696,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131359548</v>
+        <v>131359542</v>
       </c>
       <c r="B11" t="n">
-        <v>79266</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,21 +1655,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1734,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488187</v>
+        <v>488198</v>
       </c>
       <c r="R11" t="n">
-        <v>7036101</v>
+        <v>7036091</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,6 +1733,21 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1802,32 +1765,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131359545</v>
+        <v>131359541</v>
       </c>
       <c r="B12" t="n">
-        <v>79266</v>
+        <v>80336</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488254</v>
+        <v>488134</v>
       </c>
       <c r="R12" t="n">
-        <v>7036203</v>
+        <v>7036157</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,6 +1854,21 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1911,7 +1889,7 @@
         <v>131359534</v>
       </c>
       <c r="B13" t="n">
-        <v>57904</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,10 +2016,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131359547</v>
+        <v>131359539</v>
       </c>
       <c r="B14" t="n">
-        <v>79266</v>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,37 +2027,50 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stor-Kalvsberget Norra, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488171</v>
+        <v>488192</v>
       </c>
       <c r="R14" t="n">
-        <v>7036186</v>
+        <v>7036152</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2114,13 +2105,17 @@
           <t>2026-02-20</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1 födosökande talltita i lämplig häckbiotop.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2144,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131359542</v>
+        <v>90569298</v>
       </c>
       <c r="B15" t="n">
-        <v>79023</v>
+        <v>109815</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2155,37 +2150,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>220204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stor-Kalvsberget Norra, Jmt</t>
+          <t>Husås – Andviken – väg Z751, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488198</v>
+        <v>488364</v>
       </c>
       <c r="R15" t="n">
-        <v>7036091</v>
+        <v>7036217</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2212,12 +2204,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2020-07-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2020-07-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Allmän</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2226,42 +2223,160 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Leif Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Emma Karlsson, Therese Kalling</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131359540</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stor-Kalvsberget Norra, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>488103</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7036077</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På bark av tall.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3512-2026 artfynd.xlsx
+++ b/artfynd/A 3512-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131359543</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131359545</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131359546</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131359547</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131359548</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131359549</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131359550</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131359553</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1641,6 +1686,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131359533</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,6 +1812,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131359542</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1883,6 +1938,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131359541</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2013,6 +2073,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131359534</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2136,6 +2201,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131359539</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2247,6 +2317,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90569298</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2377,8 +2452,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131359540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>